--- a/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-31 - 2026-09-06).xlsx
+++ b/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-31 - 2026-09-06).xlsx
@@ -227,22 +227,22 @@
     <t>22</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>R$ 58.200,59</t>
-  </si>
-  <si>
-    <t>622.2</t>
-  </si>
-  <si>
-    <t>411.3</t>
-  </si>
-  <si>
-    <t>6.34</t>
-  </si>
-  <si>
-    <t>17.5</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>R$ 58.513,99</t>
+  </si>
+  <si>
+    <t>629.4</t>
+  </si>
+  <si>
+    <t>432.3</t>
+  </si>
+  <si>
+    <t>6.35</t>
+  </si>
+  <si>
+    <t>17.6</t>
   </si>
   <si>
     <t>4.2</t>
@@ -251,10 +251,10 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>46.3%</t>
-  </si>
-  <si>
-    <t>13.8%</t>
+    <t>44.3%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -263,22 +263,22 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>5.2%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>4.3%</t>
   </si>
   <si>
-    <t>1355.0</t>
-  </si>
-  <si>
-    <t>1193.0</t>
+    <t>1397.0</t>
+  </si>
+  <si>
+    <t>1231.0</t>
   </si>
   <si>
     <t>23.0</t>
@@ -287,19 +287,22 @@
     <t>4.0</t>
   </si>
   <si>
-    <t>99.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>456.0</t>
-  </si>
-  <si>
-    <t>221.0</t>
-  </si>
-  <si>
-    <t>372.0</t>
+    <t>105.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>469.0</t>
+  </si>
+  <si>
+    <t>226.0</t>
+  </si>
+  <si>
+    <t>388.0</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -1277,7 +1280,7 @@
         <v>636</v>
       </c>
       <c r="O4" s="6">
-        <v>179</v>
+        <v>490</v>
       </c>
       <c r="P4" s="7">
         <v>7.7948881789137383</v>
@@ -1295,7 +1298,7 @@
         <v>0.44171779141104295</v>
       </c>
       <c r="U4" s="9">
-        <v>0.10614525139664804</v>
+        <v>0.075510204081632656</v>
       </c>
       <c r="V4" s="9">
         <v>0</v>
@@ -1304,52 +1307,52 @@
         <v>0</v>
       </c>
       <c r="X4" s="9">
-        <v>0.0111731843575419</v>
+        <v>0.012244897959183673</v>
       </c>
       <c r="Y4" s="9">
-        <v>0</v>
+        <v>0.0020408163265306124</v>
       </c>
       <c r="Z4" s="9">
-        <v>0.0111731843575419</v>
+        <v>0.0061224489795918364</v>
       </c>
       <c r="AA4" s="9">
-        <v>0.061452513966480445</v>
+        <v>0.038775510204081633</v>
       </c>
       <c r="AB4" s="9">
-        <v>0.0111731843575419</v>
+        <v>0.0081632653061224497</v>
       </c>
       <c r="AC4" s="9">
-        <v>0.0223463687150838</v>
+        <v>0.016326530612244899</v>
       </c>
       <c r="AD4" s="6">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AE4" s="6">
+        <v>37</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="6">
         <v>19</v>
       </c>
-      <c r="AF4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="6">
-        <v>2</v>
-      </c>
-      <c r="AK4" s="6">
-        <v>11</v>
-      </c>
       <c r="AL4" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN4" s="9">
         <v>0</v>
@@ -3511,7 +3514,7 @@
         <v>19714</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>51</v>
@@ -3542,61 +3545,61 @@
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="5">
-        <v>55285.556666666664</v>
+        <v>62149.119999999995</v>
       </c>
       <c r="N19" s="6">
-        <v>491</v>
+        <v>641</v>
       </c>
       <c r="O19" s="6">
-        <v>361</v>
+        <v>490</v>
       </c>
       <c r="P19" s="7">
-        <v>6.5235311475409841</v>
+        <v>6.8271351562499998</v>
       </c>
       <c r="Q19" s="8">
-        <v>17.297539275766017</v>
+        <v>18.238592827868853</v>
       </c>
       <c r="R19" s="8">
-        <v>3.7139904225352112</v>
+        <v>4.3805206249999999</v>
       </c>
       <c r="S19" s="8">
         <v>7</v>
       </c>
       <c r="T19" s="9">
-        <v>0.49860724233983289</v>
+        <v>0.42622950819672129</v>
       </c>
       <c r="U19" s="9">
-        <v>0.085872576177285317</v>
+        <v>0.10408163265306122</v>
       </c>
       <c r="V19" s="9">
-        <v>0.011080332409972299</v>
+        <v>0.0081632653061224497</v>
       </c>
       <c r="W19" s="9">
         <v>0</v>
       </c>
       <c r="X19" s="9">
-        <v>0.013850415512465374</v>
+        <v>0.014285714285714285</v>
       </c>
       <c r="Y19" s="9">
         <v>0</v>
       </c>
       <c r="Z19" s="9">
-        <v>0.0027700831024930748</v>
+        <v>0.0020408163265306124</v>
       </c>
       <c r="AA19" s="9">
-        <v>0.027700831024930747</v>
+        <v>0.030612244897959183</v>
       </c>
       <c r="AB19" s="9">
-        <v>0.019390581717451522</v>
+        <v>0.020408163265306121</v>
       </c>
       <c r="AC19" s="9">
-        <v>0.01662049861495845</v>
+        <v>0.036734693877551024</v>
       </c>
       <c r="AD19" s="6">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="AE19" s="6">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="AF19" s="6">
         <v>4</v>
@@ -3605,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI19" s="6">
         <v>0</v>
@@ -3614,13 +3617,13 @@
         <v>1</v>
       </c>
       <c r="AK19" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL19" s="6">
         <v>10</v>
       </c>
-      <c r="AL19" s="6">
-        <v>7</v>
-      </c>
       <c r="AM19" s="6">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -4370,22 +4373,22 @@
         <v>93</v>
       </c>
       <c t="s" r="AJ24" s="11">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c t="s" r="AK24" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="AL24" s="11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="AM24" s="11">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="AN24" s="11">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="AO24" s="11">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AP24" s="12"/>
       <c t="s" r="AQ24" s="12">
@@ -4402,10 +4405,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX24" s="11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="AY24" s="11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AZ24" s="12"/>
       <c r="BA24" s="12"/>
